--- a/TEXTRADE/TEXTRADE/DOCUMENTATION/MMC/GREY STOCK.xlsx
+++ b/TEXTRADE/TEXTRADE/DOCUMENTATION/MMC/GREY STOCK.xlsx
@@ -3,17 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD531EF2-624E-4932-8D5B-FA4F260B57D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FB35F2-A154-49BF-B089-30372B57C76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GREY" sheetId="1" r:id="rId1"/>
-    <sheet name="FINISH" sheetId="10" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FINISH!$A$1:$O$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GREY!$A$1:$O$1048575</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$O$137</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -650,7 +650,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
